--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ec66d29316e63c22/桌面/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ec66d29316e63c22/桌面/瑪奇/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{977C4A75-32B6-4F2F-8798-25CED85A8D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E77EC16A-1B70-4069-98DB-10AF212CF5E8}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{5B11DBF4-A52C-42EF-850B-F88D143D94A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C4ADDD9-B36E-4F94-AD4E-04F13CA34BE9}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{B044D872-9C69-4966-96BD-21BAC6DBCF5C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="130">
   <si>
     <t>加工品</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -391,14 +391,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>推薦</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>★</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>伊比</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -512,6 +504,46 @@
   </si>
   <si>
     <t>高級煉金術再燃燒催化劑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>貓商人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>狩獵場、副本</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>擠著吃的點心</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>繃帶</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢復藥水</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>血紅藥草</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新芽蘑菇</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鹽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>糖</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>高麗菜</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -519,7 +551,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -552,76 +584,6 @@
     </font>
     <font>
       <sz val="16"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FFFF33CC"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FF00B0F0"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="5"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FF00B050"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FF0070C0"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FF7030A0"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="7" tint="-0.249977111117893"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FFFF0066"/>
       <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -772,7 +734,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -812,17 +774,47 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -833,131 +825,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1278,42 +1153,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5D330BC-B3D7-4A64-AF80-F838651FC966}">
-  <dimension ref="A1:J56"/>
-  <sheetFormatPr defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I61"/>
+  <sheetFormatPr defaultRowHeight="21.1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21" style="53" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9" style="53"/>
-    <col min="4" max="4" width="15.875" style="53" customWidth="1"/>
-    <col min="5" max="5" width="14.375" style="53" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8" style="53" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.875" style="53" customWidth="1"/>
-    <col min="8" max="8" width="8" style="57" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="34.5" style="53" customWidth="1"/>
-    <col min="10" max="10" width="8" style="57" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9" style="53"/>
-    <col min="12" max="12" width="31.75" style="53" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="53"/>
+    <col min="1" max="1" width="21" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9" style="3"/>
+    <col min="4" max="4" width="21" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.5" style="3" customWidth="1"/>
+    <col min="9" max="9" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" style="3"/>
+    <col min="11" max="11" width="31.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22.45" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:9" ht="22.45" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="23"/>
-    </row>
-    <row r="2" spans="1:10" ht="21.75" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="32"/>
+    </row>
+    <row r="2" spans="1:9" ht="21.75" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B3" s="5"/>
     </row>
-    <row r="4" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>89</v>
       </c>
@@ -1321,27 +1195,19 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B5" s="32"/>
+      <c r="B5" s="15"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10" ht="22.45" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:9" ht="22.45" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C6" s="1"/>
       <c r="D6" s="7" t="s">
         <v>1</v>
@@ -1350,1114 +1216,1100 @@
         <v>2</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="H6" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="I6" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="I6" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="J6" s="24" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="21.75" thickTop="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:9" ht="21.75" thickTop="1" x14ac:dyDescent="0.3">
       <c r="C7" s="4"/>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G7" s="42" t="s">
+      <c r="F7" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="49">
-        <v>10</v>
-      </c>
-      <c r="I7" s="8" t="s">
+      <c r="G7" s="13">
+        <v>10</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="J7" s="35">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="I7" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C8" s="1"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G8" s="43" t="s">
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="35">
-        <v>10</v>
-      </c>
-      <c r="I8" s="11" t="s">
+      <c r="G8" s="9">
+        <v>10</v>
+      </c>
+      <c r="H8" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="J8" s="35">
+      <c r="I8" s="9">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C9" s="4"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="25" t="s">
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="37">
-        <v>1</v>
-      </c>
-      <c r="I9" s="12" t="s">
+      <c r="G9" s="9">
+        <v>1</v>
+      </c>
+      <c r="H9" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="J9" s="35">
+      <c r="I9" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C10" s="4"/>
-      <c r="D10" s="19"/>
+      <c r="D10" s="29"/>
       <c r="E10" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="F10" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="35">
+      <c r="G10" s="9">
         <v>8</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="H10" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="J10" s="35">
+      <c r="I10" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="17" t="s">
+      <c r="D11" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="29" t="s">
+      <c r="F11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="38">
-        <v>1</v>
-      </c>
-      <c r="I11" s="13" t="s">
+      <c r="G11" s="9">
+        <v>1</v>
+      </c>
+      <c r="H11" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="J11" s="35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="I11" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="29" t="s">
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="H12" s="38">
-        <v>1</v>
-      </c>
-      <c r="I12" s="13" t="s">
+      <c r="G12" s="9">
+        <v>1</v>
+      </c>
+      <c r="H12" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="J12" s="35">
+      <c r="I12" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17" t="s">
+      <c r="D13" s="27"/>
+      <c r="E13" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G13" s="44" t="s">
+      <c r="F13" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="36">
+      <c r="G13" s="9">
         <v>12</v>
       </c>
-      <c r="I13" s="25" t="s">
+      <c r="H13" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="J13" s="35">
+      <c r="I13" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="34" t="s">
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="36">
+      <c r="G14" s="9">
         <v>2</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="H14" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="J14" s="35">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="I14" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17" t="s">
+      <c r="D15" s="27"/>
+      <c r="E15" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G15" s="44" t="s">
+      <c r="F15" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="36">
+      <c r="G15" s="9">
         <v>8</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="H15" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="J15" s="35">
+      <c r="I15" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G16" s="44" t="s">
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="36">
+      <c r="G16" s="9">
         <v>4</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="H16" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="J16" s="35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="I16" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17" t="s">
+      <c r="D17" s="27"/>
+      <c r="E17" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G17" s="44" t="s">
+      <c r="F17" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="36">
+      <c r="G17" s="9">
         <v>8</v>
       </c>
-      <c r="I17" s="13" t="s">
+      <c r="H17" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="J17" s="35">
+      <c r="I17" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G18" s="44" t="s">
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="H18" s="36">
+      <c r="G18" s="9">
         <v>4</v>
       </c>
-      <c r="I18" s="13" t="s">
+      <c r="H18" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="J18" s="35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="I18" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="20" t="s">
+      <c r="D19" s="27"/>
+      <c r="E19" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G19" s="44" t="s">
+      <c r="F19" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H19" s="36">
-        <v>10</v>
-      </c>
-      <c r="I19" s="29" t="s">
+      <c r="G19" s="9">
+        <v>10</v>
+      </c>
+      <c r="H19" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="J19" s="35">
+      <c r="I19" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="59"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="58" t="s">
+      <c r="D20" s="27"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="G20" s="9">
+        <v>3</v>
+      </c>
+      <c r="H20" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="H20" s="36">
-        <v>3</v>
-      </c>
-      <c r="I20" s="58" t="s">
-        <v>115</v>
-      </c>
-      <c r="J20" s="35">
+      <c r="I20" s="9">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="58" t="s">
-        <v>114</v>
-      </c>
-      <c r="H21" s="36">
+      <c r="D21" s="27"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="G21" s="9">
         <v>2</v>
       </c>
-      <c r="I21" s="58" t="s">
-        <v>115</v>
-      </c>
-      <c r="J21" s="35">
+      <c r="H21" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="I21" s="9">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
-      <c r="D22" s="17"/>
+      <c r="D22" s="27"/>
       <c r="E22" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F22" s="10"/>
-      <c r="G22" s="26" t="s">
+      <c r="F22" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="H22" s="39">
-        <v>1</v>
-      </c>
-      <c r="I22" s="29" t="s">
+      <c r="G22" s="9">
+        <v>1</v>
+      </c>
+      <c r="H22" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="J22" s="35">
+      <c r="I22" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17" t="s">
+      <c r="D23" s="27"/>
+      <c r="E23" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G23" s="44" t="s">
+      <c r="F23" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="H23" s="36">
+      <c r="G23" s="9">
         <v>2</v>
       </c>
-      <c r="I23" s="15" t="s">
+      <c r="H23" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="J23" s="35">
+      <c r="I23" s="9">
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G24" s="46" t="s">
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H24" s="36">
-        <v>10</v>
-      </c>
-      <c r="I24" s="16" t="s">
+      <c r="G24" s="9">
+        <v>10</v>
+      </c>
+      <c r="H24" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="J24" s="35">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="I24" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
-      <c r="D25" s="17"/>
+      <c r="D25" s="27"/>
       <c r="E25" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G25" s="44" t="s">
+      <c r="F25" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="H25" s="36">
-        <v>1</v>
-      </c>
-      <c r="I25" s="13" t="s">
+      <c r="G25" s="9">
+        <v>1</v>
+      </c>
+      <c r="H25" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="J25" s="35">
+      <c r="I25" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
-      <c r="D26" s="17"/>
+      <c r="D26" s="27"/>
       <c r="E26" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F26" s="10"/>
-      <c r="G26" s="34" t="s">
+      <c r="F26" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="H26" s="36">
-        <v>10</v>
-      </c>
-      <c r="I26" s="26" t="s">
+      <c r="G26" s="9">
+        <v>10</v>
+      </c>
+      <c r="H26" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J26" s="35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="I26" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
-      <c r="D27" s="20" t="s">
+      <c r="D27" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="E27" s="20" t="s">
+      <c r="E27" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="F27" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G27" s="44" t="s">
+      <c r="F27" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="H27" s="36">
+      <c r="G27" s="9">
         <v>4</v>
       </c>
-      <c r="I27" s="15" t="s">
+      <c r="H27" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="J27" s="35">
+      <c r="I27" s="9">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
-      <c r="D28" s="59"/>
-      <c r="E28" s="59"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="H28" s="36">
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="G28" s="9">
         <v>30</v>
       </c>
-      <c r="I28" s="46" t="s">
-        <v>118</v>
-      </c>
-      <c r="J28" s="35">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="H28" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="I28" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
-      <c r="D29" s="59"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="46" t="s">
-        <v>119</v>
-      </c>
-      <c r="H29" s="36">
-        <v>10</v>
-      </c>
-      <c r="I29" s="46" t="s">
-        <v>118</v>
-      </c>
-      <c r="J29" s="35">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="D29" s="24"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="G29" s="9">
+        <v>10</v>
+      </c>
+      <c r="H29" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="I29" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
-      <c r="D30" s="59"/>
-      <c r="E30" s="17" t="s">
+      <c r="D30" s="24"/>
+      <c r="E30" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="F30" s="10"/>
-      <c r="G30" s="44" t="s">
+      <c r="F30" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H30" s="36">
-        <v>1</v>
-      </c>
-      <c r="I30" s="16" t="s">
+      <c r="G30" s="9">
+        <v>1</v>
+      </c>
+      <c r="H30" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="J30" s="35">
+      <c r="I30" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="59"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="47" t="s">
+      <c r="D31" s="24"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="H31" s="33">
-        <v>1</v>
-      </c>
-      <c r="I31" s="16" t="s">
+      <c r="G31" s="9">
+        <v>1</v>
+      </c>
+      <c r="H31" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="J31" s="35">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="I31" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="59"/>
+      <c r="D32" s="24"/>
       <c r="E32" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F32" s="10"/>
-      <c r="G32" s="46" t="s">
+      <c r="F32" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="H32" s="36">
+      <c r="G32" s="9">
         <v>40</v>
       </c>
-      <c r="I32" s="60" t="s">
+      <c r="H32" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="J32" s="35">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="I32" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="59"/>
-      <c r="E33" s="17" t="s">
+      <c r="D33" s="24"/>
+      <c r="E33" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="F33" s="10"/>
-      <c r="G33" s="34" t="s">
+      <c r="F33" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="H33" s="36">
-        <v>1</v>
-      </c>
-      <c r="I33" s="11" t="s">
+      <c r="G33" s="9">
+        <v>1</v>
+      </c>
+      <c r="H33" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="J33" s="35">
+      <c r="I33" s="9">
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="59"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="28" t="s">
+      <c r="D34" s="24"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="H34" s="40">
-        <v>1</v>
-      </c>
-      <c r="I34" s="11" t="s">
+      <c r="G34" s="9">
+        <v>1</v>
+      </c>
+      <c r="H34" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="J34" s="35">
+      <c r="I34" s="9">
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="59"/>
+      <c r="D35" s="24"/>
       <c r="E35" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F35" s="10"/>
-      <c r="G35" s="44" t="s">
+      <c r="F35" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="H35" s="36">
+      <c r="G35" s="9">
         <v>3</v>
       </c>
-      <c r="I35" s="27" t="s">
+      <c r="H35" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="J35" s="35">
+      <c r="I35" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="59"/>
+      <c r="D36" s="24"/>
       <c r="E36" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F36" s="10"/>
-      <c r="G36" s="30" t="s">
+      <c r="F36" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="H36" s="41">
+      <c r="G36" s="9">
         <v>3</v>
       </c>
-      <c r="I36" s="11" t="s">
+      <c r="H36" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="J36" s="35">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="I36" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
-      <c r="D37" s="59"/>
+      <c r="D37" s="24"/>
       <c r="E37" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F37" s="10"/>
-      <c r="G37" s="34" t="s">
+      <c r="F37" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="H37" s="36">
-        <v>1</v>
-      </c>
-      <c r="I37" s="31" t="s">
+      <c r="G37" s="9">
+        <v>1</v>
+      </c>
+      <c r="H37" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="J37" s="35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="I37" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
-      <c r="D38" s="59"/>
+      <c r="D38" s="24"/>
       <c r="E38" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F38" s="10"/>
-      <c r="G38" s="34" t="s">
+      <c r="F38" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="H38" s="36">
-        <v>10</v>
-      </c>
-      <c r="I38" s="31" t="s">
+      <c r="G38" s="9">
+        <v>10</v>
+      </c>
+      <c r="H38" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="J38" s="35">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="I38" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
-      <c r="D39" s="59"/>
+      <c r="D39" s="24"/>
       <c r="E39" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G39" s="44" t="s">
+      <c r="F39" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="H39" s="36">
-        <v>1</v>
-      </c>
-      <c r="I39" s="13" t="s">
+      <c r="G39" s="9">
+        <v>1</v>
+      </c>
+      <c r="H39" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="J39" s="35">
+      <c r="I39" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
-      <c r="D40" s="59"/>
-      <c r="E40" s="20" t="s">
+      <c r="D40" s="24"/>
+      <c r="E40" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="F40" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G40" s="61" t="s">
-        <v>121</v>
-      </c>
-      <c r="H40" s="36">
-        <v>1</v>
-      </c>
-      <c r="I40" s="13" t="s">
+      <c r="F40" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="G40" s="9">
+        <v>1</v>
+      </c>
+      <c r="H40" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="J40" s="35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="I40" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
-      <c r="D41" s="59"/>
-      <c r="E41" s="59"/>
-      <c r="F41" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G41" s="61"/>
-      <c r="H41" s="36">
-        <v>1</v>
-      </c>
-      <c r="I41" s="48" t="s">
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="9">
+        <v>1</v>
+      </c>
+      <c r="H41" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="J41" s="35">
+      <c r="I41" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G42" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="H42" s="36">
-        <v>1</v>
-      </c>
-      <c r="I42" s="54" t="s">
-        <v>121</v>
-      </c>
-      <c r="J42" s="35">
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="G42" s="9">
+        <v>1</v>
+      </c>
+      <c r="H42" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="I42" s="9">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
-      <c r="D43" s="17" t="s">
+      <c r="D43" s="27" t="s">
         <v>54</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G43" s="45" t="s">
+      <c r="F43" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="H43" s="36">
-        <v>10</v>
-      </c>
-      <c r="I43" s="13" t="s">
+      <c r="G43" s="9">
+        <v>10</v>
+      </c>
+      <c r="H43" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="J43" s="35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="I43" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17" t="s">
+      <c r="D44" s="27"/>
+      <c r="E44" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="F44" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G44" s="45"/>
-      <c r="H44" s="36">
-        <v>1</v>
-      </c>
-      <c r="I44" s="15" t="s">
+      <c r="F44" s="26"/>
+      <c r="G44" s="9">
+        <v>1</v>
+      </c>
+      <c r="H44" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="J44" s="35">
+      <c r="I44" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G45" s="45"/>
-      <c r="H45" s="36">
-        <v>1</v>
-      </c>
-      <c r="I45" s="15" t="s">
+      <c r="D45" s="27"/>
+      <c r="E45" s="27"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="9">
+        <v>1</v>
+      </c>
+      <c r="H45" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="J45" s="35">
+      <c r="I45" s="9">
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
-      <c r="D46" s="17"/>
+      <c r="D46" s="27"/>
       <c r="E46" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="F46" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="G46" s="9">
+        <v>10</v>
+      </c>
+      <c r="H46" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="F46" s="10"/>
-      <c r="G46" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="H46" s="36">
-        <v>10</v>
-      </c>
-      <c r="I46" s="52" t="s">
-        <v>95</v>
-      </c>
-      <c r="J46" s="35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="I46" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
-      <c r="D47" s="17"/>
+      <c r="D47" s="27"/>
       <c r="E47" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G47" s="44" t="s">
+      <c r="F47" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="H47" s="36">
+      <c r="G47" s="9">
         <v>6</v>
       </c>
-      <c r="I47" s="13" t="s">
+      <c r="H47" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="J47" s="35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="21.1" x14ac:dyDescent="0.3">
+      <c r="I47" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
-      <c r="D48" s="17"/>
+      <c r="D48" s="27"/>
       <c r="E48" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F48" s="10"/>
-      <c r="G48" s="46" t="s">
+      <c r="F48" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="H48" s="36">
+      <c r="G48" s="9">
         <v>15</v>
       </c>
-      <c r="I48" s="16" t="s">
+      <c r="H48" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="J48" s="35">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="4:10" ht="21.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D49" s="17"/>
-      <c r="E49" s="51" t="s">
+      <c r="I48" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="4:9" ht="21.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D49" s="27"/>
+      <c r="E49" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="F49" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G49" s="9">
+        <v>5</v>
+      </c>
+      <c r="H49" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="F49" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G49" s="44" t="s">
+      <c r="I49" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="H49" s="10">
+      <c r="G50" s="9">
+        <v>1</v>
+      </c>
+      <c r="H50" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="I50" s="10">
         <v>5</v>
       </c>
-      <c r="I49" s="44" t="s">
+    </row>
+    <row r="51" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D51" s="27"/>
+      <c r="E51" s="27"/>
+      <c r="F51" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G51" s="9">
+        <v>1</v>
+      </c>
+      <c r="H51" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="J49" s="10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="4:10" ht="21.1" x14ac:dyDescent="0.3">
-      <c r="D50" s="17"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="H50" s="10">
-        <v>1</v>
-      </c>
-      <c r="I50" s="16" t="s">
+      <c r="I51" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="4:9" ht="21.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D52" s="27"/>
+      <c r="E52" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="F52" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="J50" s="10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="4:10" ht="21.1" x14ac:dyDescent="0.3">
-      <c r="D51" s="17"/>
-      <c r="E51" s="51"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="16" t="s">
+      <c r="G52" s="9">
+        <v>10</v>
+      </c>
+      <c r="H52" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="H51" s="10">
-        <v>1</v>
-      </c>
-      <c r="I51" s="16" t="s">
+      <c r="I52" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D53" s="27"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="G53" s="9">
+        <v>1</v>
+      </c>
+      <c r="H53" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="I53" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D54" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="E54" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="F54" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="G54" s="9">
+        <v>3</v>
+      </c>
+      <c r="H54" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="J51" s="10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="52" spans="4:10" ht="21.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D52" s="17"/>
-      <c r="E52" s="51" t="s">
+      <c r="I54" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D55" s="25"/>
+      <c r="E55" s="27"/>
+      <c r="F55" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="G55" s="9">
+        <v>15</v>
+      </c>
+      <c r="H55" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="F52" s="14"/>
-      <c r="G52" s="44" t="s">
-        <v>102</v>
-      </c>
-      <c r="H52" s="10">
-        <v>10</v>
-      </c>
-      <c r="I52" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="J52" s="10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="4:10" ht="21.1" x14ac:dyDescent="0.3">
-      <c r="D53" s="17"/>
-      <c r="E53" s="51"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="H53" s="10">
-        <v>1</v>
-      </c>
-      <c r="I53" s="54" t="s">
-        <v>104</v>
-      </c>
-      <c r="J53" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="4:10" ht="21.1" x14ac:dyDescent="0.3">
-      <c r="D54" s="20" t="s">
+      <c r="I55" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="4:9" ht="17" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D56" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="E56" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="E54" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="F54" s="14"/>
-      <c r="G54" s="54" t="s">
-        <v>104</v>
-      </c>
-      <c r="H54" s="10">
+      <c r="F56" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G56" s="9">
+        <v>10</v>
+      </c>
+      <c r="H56" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="I56" s="10">
         <v>3</v>
       </c>
-      <c r="I54" s="44" t="s">
-        <v>102</v>
-      </c>
-      <c r="J54" s="10">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="55" spans="4:10" ht="21.1" x14ac:dyDescent="0.3">
-      <c r="D55" s="21"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G55" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="H55" s="10">
-        <v>15</v>
-      </c>
-      <c r="I55" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="J55" s="10">
+    </row>
+    <row r="57" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D57" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="E57" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="G57" s="10">
         <v>3</v>
       </c>
-    </row>
-    <row r="56" spans="4:10" ht="17" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D56" s="55" t="s">
-        <v>110</v>
-      </c>
-      <c r="E56" s="55" t="s">
-        <v>111</v>
-      </c>
-      <c r="F56" s="55"/>
-      <c r="G56" s="60" t="s">
-        <v>76</v>
-      </c>
-      <c r="H56" s="56">
-        <v>10</v>
-      </c>
-      <c r="I56" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="J56" s="56">
+      <c r="H57" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I57" s="10">
         <v>3</v>
       </c>
     </row>
+    <row r="58" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D58" s="24"/>
+      <c r="E58" s="24"/>
+      <c r="F58" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G58" s="10">
+        <v>3</v>
+      </c>
+      <c r="H58" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="I58" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D59" s="24"/>
+      <c r="E59" s="24"/>
+      <c r="F59" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="G59" s="10">
+        <v>2</v>
+      </c>
+      <c r="H59" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="I59" s="10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D60" s="24"/>
+      <c r="E60" s="24"/>
+      <c r="F60" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G60" s="10">
+        <v>2</v>
+      </c>
+      <c r="H60" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="I60" s="10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D61" s="25"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="G61" s="10">
+        <v>2</v>
+      </c>
+      <c r="H61" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="I61" s="10">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="25">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="D43:D53"/>
+    <mergeCell ref="D54:D55"/>
     <mergeCell ref="E19:E21"/>
     <mergeCell ref="E27:E29"/>
     <mergeCell ref="E40:E42"/>
     <mergeCell ref="D27:D42"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="E49:E51"/>
-    <mergeCell ref="E52:E53"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="D43:D53"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="G43:G45"/>
+    <mergeCell ref="E57:E61"/>
+    <mergeCell ref="D57:D61"/>
+    <mergeCell ref="F43:F45"/>
     <mergeCell ref="E44:E45"/>
     <mergeCell ref="D7:D10"/>
     <mergeCell ref="E7:E9"/>
@@ -2469,7 +2321,8 @@
     <mergeCell ref="E23:E24"/>
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="E33:E34"/>
-    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="E49:E51"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ec66d29316e63c22/桌面/瑪奇/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{5B11DBF4-A52C-42EF-850B-F88D143D94A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C4ADDD9-B36E-4F94-AD4E-04F13CA34BE9}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{5B11DBF4-A52C-42EF-850B-F88D143D94A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C828D63-DFDD-406D-BD6B-ABE16ED3776D}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{B044D872-9C69-4966-96BD-21BAC6DBCF5C}"/>
   </bookViews>
@@ -804,21 +804,27 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -827,12 +833,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1170,10 +1170,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="22.45" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="32"/>
+      <c r="B1" s="24"/>
     </row>
     <row r="2" spans="1:9" ht="21.75" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7" spans="1:9" ht="21.75" thickTop="1" x14ac:dyDescent="0.3">
       <c r="C7" s="4"/>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="30" t="s">
         <v>4</v>
       </c>
       <c r="F7" s="16" t="s">
@@ -1251,8 +1251,8 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C8" s="1"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
       <c r="F8" s="17" t="s">
         <v>6</v>
       </c>
@@ -1268,8 +1268,8 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C9" s="4"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
       <c r="F9" s="18" t="s">
         <v>7</v>
       </c>
@@ -1285,7 +1285,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C10" s="4"/>
-      <c r="D10" s="29"/>
+      <c r="D10" s="31"/>
       <c r="E10" s="9" t="s">
         <v>8</v>
       </c>
@@ -1306,10 +1306,10 @@
       <c r="A11" s="1"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="27" t="s">
+      <c r="D11" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="25" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="18" t="s">
@@ -1329,8 +1329,8 @@
       <c r="A12" s="1"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
       <c r="F12" s="18" t="s">
         <v>13</v>
       </c>
@@ -1348,8 +1348,8 @@
       <c r="A13" s="1"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27" t="s">
+      <c r="D13" s="25"/>
+      <c r="E13" s="25" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="20" t="s">
@@ -1369,8 +1369,8 @@
       <c r="A14" s="1"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
       <c r="F14" s="18" t="s">
         <v>16</v>
       </c>
@@ -1388,8 +1388,8 @@
       <c r="A15" s="1"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27" t="s">
+      <c r="D15" s="25"/>
+      <c r="E15" s="25" t="s">
         <v>17</v>
       </c>
       <c r="F15" s="20" t="s">
@@ -1409,8 +1409,8 @@
       <c r="A16" s="1"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
       <c r="F16" s="20" t="s">
         <v>19</v>
       </c>
@@ -1428,8 +1428,8 @@
       <c r="A17" s="1"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27" t="s">
+      <c r="D17" s="25"/>
+      <c r="E17" s="25" t="s">
         <v>20</v>
       </c>
       <c r="F17" s="20" t="s">
@@ -1449,8 +1449,8 @@
       <c r="A18" s="1"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
       <c r="F18" s="20" t="s">
         <v>22</v>
       </c>
@@ -1468,8 +1468,8 @@
       <c r="A19" s="1"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="23" t="s">
+      <c r="D19" s="25"/>
+      <c r="E19" s="26" t="s">
         <v>23</v>
       </c>
       <c r="F19" s="20" t="s">
@@ -1489,8 +1489,8 @@
       <c r="A20" s="1"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="24"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="28"/>
       <c r="F20" s="18" t="s">
         <v>111</v>
       </c>
@@ -1508,8 +1508,8 @@
       <c r="A21" s="1"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="27"/>
       <c r="F21" s="18" t="s">
         <v>112</v>
       </c>
@@ -1527,7 +1527,7 @@
       <c r="A22" s="1"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
-      <c r="D22" s="27"/>
+      <c r="D22" s="25"/>
       <c r="E22" s="10" t="s">
         <v>25</v>
       </c>
@@ -1548,8 +1548,8 @@
       <c r="A23" s="1"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27" t="s">
+      <c r="D23" s="25"/>
+      <c r="E23" s="25" t="s">
         <v>27</v>
       </c>
       <c r="F23" s="20" t="s">
@@ -1569,8 +1569,8 @@
       <c r="A24" s="1"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
       <c r="F24" s="17" t="s">
         <v>6</v>
       </c>
@@ -1588,7 +1588,7 @@
       <c r="A25" s="1"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
-      <c r="D25" s="27"/>
+      <c r="D25" s="25"/>
       <c r="E25" s="10" t="s">
         <v>29</v>
       </c>
@@ -1609,7 +1609,7 @@
       <c r="A26" s="1"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
-      <c r="D26" s="27"/>
+      <c r="D26" s="25"/>
       <c r="E26" s="10" t="s">
         <v>31</v>
       </c>
@@ -1630,10 +1630,10 @@
       <c r="A27" s="1"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
-      <c r="D27" s="23" t="s">
+      <c r="D27" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="E27" s="23" t="s">
+      <c r="E27" s="26" t="s">
         <v>34</v>
       </c>
       <c r="F27" s="20" t="s">
@@ -1653,8 +1653,8 @@
       <c r="A28" s="1"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
       <c r="F28" s="17" t="s">
         <v>115</v>
       </c>
@@ -1672,8 +1672,8 @@
       <c r="A29" s="1"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="25"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="27"/>
       <c r="F29" s="17" t="s">
         <v>117</v>
       </c>
@@ -1691,8 +1691,8 @@
       <c r="A30" s="1"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="27" t="s">
+      <c r="D30" s="28"/>
+      <c r="E30" s="25" t="s">
         <v>36</v>
       </c>
       <c r="F30" s="20" t="s">
@@ -1712,8 +1712,8 @@
       <c r="A31" s="1"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="27"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="25"/>
       <c r="F31" s="17" t="s">
         <v>38</v>
       </c>
@@ -1731,7 +1731,7 @@
       <c r="A32" s="1"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="24"/>
+      <c r="D32" s="28"/>
       <c r="E32" s="10" t="s">
         <v>39</v>
       </c>
@@ -1752,8 +1752,8 @@
       <c r="A33" s="1"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="27" t="s">
+      <c r="D33" s="28"/>
+      <c r="E33" s="25" t="s">
         <v>41</v>
       </c>
       <c r="F33" s="18" t="s">
@@ -1773,8 +1773,8 @@
       <c r="A34" s="1"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="27"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="25"/>
       <c r="F34" s="18" t="s">
         <v>43</v>
       </c>
@@ -1792,7 +1792,7 @@
       <c r="A35" s="1"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="24"/>
+      <c r="D35" s="28"/>
       <c r="E35" s="10" t="s">
         <v>44</v>
       </c>
@@ -1813,7 +1813,7 @@
       <c r="A36" s="1"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="24"/>
+      <c r="D36" s="28"/>
       <c r="E36" s="10" t="s">
         <v>46</v>
       </c>
@@ -1834,7 +1834,7 @@
       <c r="A37" s="1"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
-      <c r="D37" s="24"/>
+      <c r="D37" s="28"/>
       <c r="E37" s="10" t="s">
         <v>48</v>
       </c>
@@ -1855,7 +1855,7 @@
       <c r="A38" s="1"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
-      <c r="D38" s="24"/>
+      <c r="D38" s="28"/>
       <c r="E38" s="10" t="s">
         <v>50</v>
       </c>
@@ -1876,7 +1876,7 @@
       <c r="A39" s="1"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
-      <c r="D39" s="24"/>
+      <c r="D39" s="28"/>
       <c r="E39" s="10" t="s">
         <v>51</v>
       </c>
@@ -1897,11 +1897,11 @@
       <c r="A40" s="1"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="23" t="s">
+      <c r="D40" s="28"/>
+      <c r="E40" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="F40" s="30" t="s">
+      <c r="F40" s="32" t="s">
         <v>119</v>
       </c>
       <c r="G40" s="9">
@@ -1918,9 +1918,9 @@
       <c r="A41" s="1"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="30"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="28"/>
+      <c r="F41" s="32"/>
       <c r="G41" s="9">
         <v>1</v>
       </c>
@@ -1935,8 +1935,8 @@
       <c r="A42" s="1"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
       <c r="F42" s="18" t="s">
         <v>118</v>
       </c>
@@ -1954,13 +1954,13 @@
       <c r="A43" s="1"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
-      <c r="D43" s="27" t="s">
+      <c r="D43" s="25" t="s">
         <v>54</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F43" s="26" t="s">
+      <c r="F43" s="29" t="s">
         <v>56</v>
       </c>
       <c r="G43" s="9">
@@ -1977,11 +1977,11 @@
       <c r="A44" s="1"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
-      <c r="D44" s="27"/>
-      <c r="E44" s="27" t="s">
+      <c r="D44" s="25"/>
+      <c r="E44" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="F44" s="26"/>
+      <c r="F44" s="29"/>
       <c r="G44" s="9">
         <v>1</v>
       </c>
@@ -1996,9 +1996,9 @@
       <c r="A45" s="1"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
-      <c r="D45" s="27"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="26"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="29"/>
       <c r="G45" s="9">
         <v>1</v>
       </c>
@@ -2013,7 +2013,7 @@
       <c r="A46" s="1"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
-      <c r="D46" s="27"/>
+      <c r="D46" s="25"/>
       <c r="E46" s="10" t="s">
         <v>91</v>
       </c>
@@ -2034,7 +2034,7 @@
       <c r="A47" s="1"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
-      <c r="D47" s="27"/>
+      <c r="D47" s="25"/>
       <c r="E47" s="10" t="s">
         <v>58</v>
       </c>
@@ -2055,7 +2055,7 @@
       <c r="A48" s="1"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
-      <c r="D48" s="27"/>
+      <c r="D48" s="25"/>
       <c r="E48" s="10" t="s">
         <v>60</v>
       </c>
@@ -2073,8 +2073,8 @@
       </c>
     </row>
     <row r="49" spans="4:9" ht="21.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D49" s="27"/>
-      <c r="E49" s="27" t="s">
+      <c r="D49" s="25"/>
+      <c r="E49" s="25" t="s">
         <v>94</v>
       </c>
       <c r="F49" s="20" t="s">
@@ -2091,8 +2091,8 @@
       </c>
     </row>
     <row r="50" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D50" s="27"/>
-      <c r="E50" s="27"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="25"/>
       <c r="F50" s="11" t="s">
         <v>97</v>
       </c>
@@ -2107,8 +2107,8 @@
       </c>
     </row>
     <row r="51" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D51" s="27"/>
-      <c r="E51" s="27"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="25"/>
       <c r="F51" s="11" t="s">
         <v>99</v>
       </c>
@@ -2123,8 +2123,8 @@
       </c>
     </row>
     <row r="52" spans="4:9" ht="21.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D52" s="27"/>
-      <c r="E52" s="27" t="s">
+      <c r="D52" s="25"/>
+      <c r="E52" s="25" t="s">
         <v>104</v>
       </c>
       <c r="F52" s="20" t="s">
@@ -2141,8 +2141,8 @@
       </c>
     </row>
     <row r="53" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D53" s="27"/>
-      <c r="E53" s="27"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="25"/>
       <c r="F53" s="18" t="s">
         <v>93</v>
       </c>
@@ -2157,10 +2157,10 @@
       </c>
     </row>
     <row r="54" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D54" s="23" t="s">
+      <c r="D54" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="E54" s="27" t="s">
+      <c r="E54" s="25" t="s">
         <v>103</v>
       </c>
       <c r="F54" s="18" t="s">
@@ -2177,8 +2177,8 @@
       </c>
     </row>
     <row r="55" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D55" s="25"/>
-      <c r="E55" s="27"/>
+      <c r="D55" s="27"/>
+      <c r="E55" s="25"/>
       <c r="F55" s="20" t="s">
         <v>105</v>
       </c>
@@ -2213,10 +2213,10 @@
       </c>
     </row>
     <row r="57" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D57" s="23" t="s">
+      <c r="D57" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="E57" s="23" t="s">
+      <c r="E57" s="26" t="s">
         <v>120</v>
       </c>
       <c r="F57" s="11" t="s">
@@ -2233,8 +2233,8 @@
       </c>
     </row>
     <row r="58" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D58" s="24"/>
-      <c r="E58" s="24"/>
+      <c r="D58" s="28"/>
+      <c r="E58" s="28"/>
       <c r="F58" s="18" t="s">
         <v>16</v>
       </c>
@@ -2249,9 +2249,9 @@
       </c>
     </row>
     <row r="59" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D59" s="24"/>
-      <c r="E59" s="24"/>
-      <c r="F59" s="12" t="s">
+      <c r="D59" s="28"/>
+      <c r="E59" s="28"/>
+      <c r="F59" s="18" t="s">
         <v>127</v>
       </c>
       <c r="G59" s="10">
@@ -2265,9 +2265,9 @@
       </c>
     </row>
     <row r="60" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D60" s="24"/>
-      <c r="E60" s="24"/>
-      <c r="F60" s="12" t="s">
+      <c r="D60" s="28"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="18" t="s">
         <v>128</v>
       </c>
       <c r="G60" s="10">
@@ -2281,9 +2281,9 @@
       </c>
     </row>
     <row r="61" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D61" s="25"/>
-      <c r="E61" s="25"/>
-      <c r="F61" s="12" t="s">
+      <c r="D61" s="27"/>
+      <c r="E61" s="27"/>
+      <c r="F61" s="18" t="s">
         <v>129</v>
       </c>
       <c r="G61" s="10">
@@ -2298,15 +2298,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="E52:E53"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="D43:D53"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="E27:E29"/>
-    <mergeCell ref="E40:E42"/>
-    <mergeCell ref="D27:D42"/>
     <mergeCell ref="E57:E61"/>
     <mergeCell ref="D57:D61"/>
     <mergeCell ref="F43:F45"/>
@@ -2323,6 +2314,15 @@
     <mergeCell ref="E33:E34"/>
     <mergeCell ref="F40:F41"/>
     <mergeCell ref="E49:E51"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="D43:D53"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="E27:E29"/>
+    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="D27:D42"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ec66d29316e63c22/桌面/瑪奇/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{5B11DBF4-A52C-42EF-850B-F88D143D94A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C828D63-DFDD-406D-BD6B-ABE16ED3776D}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{5B11DBF4-A52C-42EF-850B-F88D143D94A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41A3C457-5B59-48D5-9589-F4912BB17B49}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{B044D872-9C69-4966-96BD-21BAC6DBCF5C}"/>
+    <workbookView xWindow="5529" yWindow="2133" windowWidth="19562" windowHeight="10134" xr2:uid="{B044D872-9C69-4966-96BD-21BAC6DBCF5C}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="138">
   <si>
     <t>加工品</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -544,6 +544,38 @@
   </si>
   <si>
     <t>高麗菜</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>凱亞拉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>庫漢</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>草莓冰飲</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>高級爆擊秘藥</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿爾米斯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>白銅礦石</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>康納</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>燈籠鮟鱇</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -804,22 +836,22 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -1153,13 +1185,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5D330BC-B3D7-4A64-AF80-F838651FC966}">
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr defaultRowHeight="21.1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="9" style="3"/>
-    <col min="4" max="4" width="21" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="34.875" style="3" customWidth="1"/>
     <col min="7" max="7" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="34.5" style="3" customWidth="1"/>
@@ -1170,10 +1202,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="22.45" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="24"/>
+      <c r="B1" s="28"/>
     </row>
     <row r="2" spans="1:9" ht="21.75" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1193,8 +1225,6 @@
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -1203,8 +1233,6 @@
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:9" ht="22.45" thickBot="1" x14ac:dyDescent="0.35">
@@ -1306,10 +1334,10 @@
       <c r="A11" s="1"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="25" t="s">
+      <c r="D11" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="23" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="18" t="s">
@@ -1329,8 +1357,8 @@
       <c r="A12" s="1"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
       <c r="F12" s="18" t="s">
         <v>13</v>
       </c>
@@ -1348,8 +1376,8 @@
       <c r="A13" s="1"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25" t="s">
+      <c r="D13" s="23"/>
+      <c r="E13" s="23" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="20" t="s">
@@ -1369,8 +1397,8 @@
       <c r="A14" s="1"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
       <c r="F14" s="18" t="s">
         <v>16</v>
       </c>
@@ -1388,8 +1416,8 @@
       <c r="A15" s="1"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25" t="s">
+      <c r="D15" s="23"/>
+      <c r="E15" s="23" t="s">
         <v>17</v>
       </c>
       <c r="F15" s="20" t="s">
@@ -1409,8 +1437,8 @@
       <c r="A16" s="1"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
       <c r="F16" s="20" t="s">
         <v>19</v>
       </c>
@@ -1428,8 +1456,8 @@
       <c r="A17" s="1"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25" t="s">
+      <c r="D17" s="23"/>
+      <c r="E17" s="23" t="s">
         <v>20</v>
       </c>
       <c r="F17" s="20" t="s">
@@ -1449,8 +1477,8 @@
       <c r="A18" s="1"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
       <c r="F18" s="20" t="s">
         <v>22</v>
       </c>
@@ -1468,8 +1496,8 @@
       <c r="A19" s="1"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="26" t="s">
+      <c r="D19" s="23"/>
+      <c r="E19" s="24" t="s">
         <v>23</v>
       </c>
       <c r="F19" s="20" t="s">
@@ -1489,8 +1517,8 @@
       <c r="A20" s="1"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="28"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="25"/>
       <c r="F20" s="18" t="s">
         <v>111</v>
       </c>
@@ -1508,8 +1536,8 @@
       <c r="A21" s="1"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="27"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="26"/>
       <c r="F21" s="18" t="s">
         <v>112</v>
       </c>
@@ -1527,7 +1555,7 @@
       <c r="A22" s="1"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
-      <c r="D22" s="25"/>
+      <c r="D22" s="23"/>
       <c r="E22" s="10" t="s">
         <v>25</v>
       </c>
@@ -1548,8 +1576,8 @@
       <c r="A23" s="1"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25" t="s">
+      <c r="D23" s="23"/>
+      <c r="E23" s="23" t="s">
         <v>27</v>
       </c>
       <c r="F23" s="20" t="s">
@@ -1569,8 +1597,8 @@
       <c r="A24" s="1"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
       <c r="F24" s="17" t="s">
         <v>6</v>
       </c>
@@ -1588,7 +1616,7 @@
       <c r="A25" s="1"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
-      <c r="D25" s="25"/>
+      <c r="D25" s="23"/>
       <c r="E25" s="10" t="s">
         <v>29</v>
       </c>
@@ -1609,7 +1637,7 @@
       <c r="A26" s="1"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
-      <c r="D26" s="25"/>
+      <c r="D26" s="23"/>
       <c r="E26" s="10" t="s">
         <v>31</v>
       </c>
@@ -1630,10 +1658,10 @@
       <c r="A27" s="1"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
-      <c r="D27" s="26" t="s">
+      <c r="D27" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="E27" s="26" t="s">
+      <c r="E27" s="24" t="s">
         <v>34</v>
       </c>
       <c r="F27" s="20" t="s">
@@ -1653,8 +1681,8 @@
       <c r="A28" s="1"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
       <c r="F28" s="17" t="s">
         <v>115</v>
       </c>
@@ -1672,8 +1700,8 @@
       <c r="A29" s="1"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="27"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="26"/>
       <c r="F29" s="17" t="s">
         <v>117</v>
       </c>
@@ -1691,8 +1719,8 @@
       <c r="A30" s="1"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="25" t="s">
+      <c r="D30" s="25"/>
+      <c r="E30" s="23" t="s">
         <v>36</v>
       </c>
       <c r="F30" s="20" t="s">
@@ -1712,8 +1740,8 @@
       <c r="A31" s="1"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="23"/>
       <c r="F31" s="17" t="s">
         <v>38</v>
       </c>
@@ -1731,7 +1759,7 @@
       <c r="A32" s="1"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="28"/>
+      <c r="D32" s="25"/>
       <c r="E32" s="10" t="s">
         <v>39</v>
       </c>
@@ -1752,8 +1780,8 @@
       <c r="A33" s="1"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="25" t="s">
+      <c r="D33" s="25"/>
+      <c r="E33" s="23" t="s">
         <v>41</v>
       </c>
       <c r="F33" s="18" t="s">
@@ -1773,8 +1801,8 @@
       <c r="A34" s="1"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="23"/>
       <c r="F34" s="18" t="s">
         <v>43</v>
       </c>
@@ -1792,7 +1820,7 @@
       <c r="A35" s="1"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="28"/>
+      <c r="D35" s="25"/>
       <c r="E35" s="10" t="s">
         <v>44</v>
       </c>
@@ -1813,7 +1841,7 @@
       <c r="A36" s="1"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="28"/>
+      <c r="D36" s="25"/>
       <c r="E36" s="10" t="s">
         <v>46</v>
       </c>
@@ -1834,7 +1862,7 @@
       <c r="A37" s="1"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
-      <c r="D37" s="28"/>
+      <c r="D37" s="25"/>
       <c r="E37" s="10" t="s">
         <v>48</v>
       </c>
@@ -1855,7 +1883,7 @@
       <c r="A38" s="1"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
-      <c r="D38" s="28"/>
+      <c r="D38" s="25"/>
       <c r="E38" s="10" t="s">
         <v>50</v>
       </c>
@@ -1876,7 +1904,7 @@
       <c r="A39" s="1"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
-      <c r="D39" s="28"/>
+      <c r="D39" s="25"/>
       <c r="E39" s="10" t="s">
         <v>51</v>
       </c>
@@ -1897,8 +1925,8 @@
       <c r="A40" s="1"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="26" t="s">
+      <c r="D40" s="25"/>
+      <c r="E40" s="24" t="s">
         <v>53</v>
       </c>
       <c r="F40" s="32" t="s">
@@ -1918,8 +1946,8 @@
       <c r="A41" s="1"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
       <c r="F41" s="32"/>
       <c r="G41" s="9">
         <v>1</v>
@@ -1935,8 +1963,8 @@
       <c r="A42" s="1"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
       <c r="F42" s="18" t="s">
         <v>118</v>
       </c>
@@ -1954,7 +1982,7 @@
       <c r="A43" s="1"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
-      <c r="D43" s="25" t="s">
+      <c r="D43" s="23" t="s">
         <v>54</v>
       </c>
       <c r="E43" s="10" t="s">
@@ -1977,8 +2005,8 @@
       <c r="A44" s="1"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="25" t="s">
+      <c r="D44" s="23"/>
+      <c r="E44" s="23" t="s">
         <v>57</v>
       </c>
       <c r="F44" s="29"/>
@@ -1996,8 +2024,8 @@
       <c r="A45" s="1"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
-      <c r="D45" s="25"/>
-      <c r="E45" s="25"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="23"/>
       <c r="F45" s="29"/>
       <c r="G45" s="9">
         <v>1</v>
@@ -2013,7 +2041,7 @@
       <c r="A46" s="1"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
-      <c r="D46" s="25"/>
+      <c r="D46" s="23"/>
       <c r="E46" s="10" t="s">
         <v>91</v>
       </c>
@@ -2034,7 +2062,7 @@
       <c r="A47" s="1"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
-      <c r="D47" s="25"/>
+      <c r="D47" s="23"/>
       <c r="E47" s="10" t="s">
         <v>58</v>
       </c>
@@ -2055,7 +2083,7 @@
       <c r="A48" s="1"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
-      <c r="D48" s="25"/>
+      <c r="D48" s="23"/>
       <c r="E48" s="10" t="s">
         <v>60</v>
       </c>
@@ -2073,8 +2101,8 @@
       </c>
     </row>
     <row r="49" spans="4:9" ht="21.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D49" s="25"/>
-      <c r="E49" s="25" t="s">
+      <c r="D49" s="23"/>
+      <c r="E49" s="23" t="s">
         <v>94</v>
       </c>
       <c r="F49" s="20" t="s">
@@ -2091,8 +2119,8 @@
       </c>
     </row>
     <row r="50" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D50" s="25"/>
-      <c r="E50" s="25"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="23"/>
       <c r="F50" s="11" t="s">
         <v>97</v>
       </c>
@@ -2107,8 +2135,8 @@
       </c>
     </row>
     <row r="51" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D51" s="25"/>
-      <c r="E51" s="25"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="23"/>
       <c r="F51" s="11" t="s">
         <v>99</v>
       </c>
@@ -2123,8 +2151,8 @@
       </c>
     </row>
     <row r="52" spans="4:9" ht="21.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D52" s="25"/>
-      <c r="E52" s="25" t="s">
+      <c r="D52" s="23"/>
+      <c r="E52" s="23" t="s">
         <v>104</v>
       </c>
       <c r="F52" s="20" t="s">
@@ -2141,8 +2169,8 @@
       </c>
     </row>
     <row r="53" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D53" s="25"/>
-      <c r="E53" s="25"/>
+      <c r="D53" s="23"/>
+      <c r="E53" s="23"/>
       <c r="F53" s="18" t="s">
         <v>93</v>
       </c>
@@ -2157,10 +2185,10 @@
       </c>
     </row>
     <row r="54" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D54" s="26" t="s">
+      <c r="D54" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="E54" s="25" t="s">
+      <c r="E54" s="23" t="s">
         <v>103</v>
       </c>
       <c r="F54" s="18" t="s">
@@ -2177,8 +2205,8 @@
       </c>
     </row>
     <row r="55" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D55" s="27"/>
-      <c r="E55" s="25"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="23"/>
       <c r="F55" s="20" t="s">
         <v>105</v>
       </c>
@@ -2213,10 +2241,10 @@
       </c>
     </row>
     <row r="57" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D57" s="26" t="s">
+      <c r="D57" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="E57" s="26" t="s">
+      <c r="E57" s="24" t="s">
         <v>120</v>
       </c>
       <c r="F57" s="11" t="s">
@@ -2233,8 +2261,8 @@
       </c>
     </row>
     <row r="58" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D58" s="28"/>
-      <c r="E58" s="28"/>
+      <c r="D58" s="25"/>
+      <c r="E58" s="25"/>
       <c r="F58" s="18" t="s">
         <v>16</v>
       </c>
@@ -2249,8 +2277,8 @@
       </c>
     </row>
     <row r="59" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D59" s="28"/>
-      <c r="E59" s="28"/>
+      <c r="D59" s="25"/>
+      <c r="E59" s="25"/>
       <c r="F59" s="18" t="s">
         <v>127</v>
       </c>
@@ -2265,8 +2293,8 @@
       </c>
     </row>
     <row r="60" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D60" s="28"/>
-      <c r="E60" s="28"/>
+      <c r="D60" s="25"/>
+      <c r="E60" s="25"/>
       <c r="F60" s="18" t="s">
         <v>128</v>
       </c>
@@ -2281,8 +2309,8 @@
       </c>
     </row>
     <row r="61" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D61" s="27"/>
-      <c r="E61" s="27"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
       <c r="F61" s="18" t="s">
         <v>129</v>
       </c>
@@ -2296,10 +2324,96 @@
         <v>100</v>
       </c>
     </row>
+    <row r="62" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D62" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="E62" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="F62" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="G62" s="10">
+        <v>50</v>
+      </c>
+      <c r="H62" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="I62" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D63" s="25"/>
+      <c r="E63" s="23"/>
+      <c r="F63" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="G63" s="10">
+        <v>1</v>
+      </c>
+      <c r="H63" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="I63" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D64" s="25"/>
+      <c r="E64" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="F64" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="G64" s="10">
+        <v>1</v>
+      </c>
+      <c r="H64" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I64" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D65" s="25"/>
+      <c r="E65" s="23"/>
+      <c r="F65" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G65" s="9">
+        <v>10</v>
+      </c>
+      <c r="H65" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="I65" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D66" s="26"/>
+      <c r="E66" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="F66" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G66" s="10">
+        <v>3</v>
+      </c>
+      <c r="H66" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="I66" s="10">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="E57:E61"/>
-    <mergeCell ref="D57:D61"/>
+  <mergeCells count="28">
     <mergeCell ref="F43:F45"/>
     <mergeCell ref="E44:E45"/>
     <mergeCell ref="D7:D10"/>
@@ -2313,7 +2427,9 @@
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="E33:E34"/>
     <mergeCell ref="F40:F41"/>
-    <mergeCell ref="E49:E51"/>
+    <mergeCell ref="E62:E63"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="D62:D66"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="E52:E53"/>
     <mergeCell ref="E54:E55"/>
@@ -2323,6 +2439,9 @@
     <mergeCell ref="E27:E29"/>
     <mergeCell ref="E40:E42"/>
     <mergeCell ref="D27:D42"/>
+    <mergeCell ref="E57:E61"/>
+    <mergeCell ref="D57:D61"/>
+    <mergeCell ref="E49:E51"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
